--- a/pages/WR_progressions/Men_TP.xlsx
+++ b/pages/WR_progressions/Men_TP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\WR progressions\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\WR_progressions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{261AF2D3-68D3-45BD-92A3-D7E5014A7A0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DE5D6C3-4EC9-4C1B-A8C1-6B8EC5AF9B4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="48765" yWindow="2250" windowWidth="15000" windowHeight="12000" xr2:uid="{5B864704-1F0A-4CFC-9A10-3E102D3244D3}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{5B864704-1F0A-4CFC-9A10-3E102D3244D3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="166" formatCode="mm:ss.000"/>
+    <numFmt numFmtId="164" formatCode="mm:ss.000"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -88,7 +88,7 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
@@ -425,7 +425,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20BEA07D-F91B-43E2-A74E-7CB853835BEE}">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="9.06640625" style="1"/>
@@ -433,7 +433,7 @@
     <col min="6" max="7" width="9.9296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -447,230 +447,229 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2" s="1">
         <v>2.8222222222222221E-3</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2">
         <f>A2*86400</f>
         <v>243.83999999999997</v>
       </c>
       <c r="C2" s="2">
         <v>34201</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2">
         <v>34201</v>
       </c>
       <c r="F2" s="2"/>
-      <c r="G2" s="3"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3" s="1">
         <v>2.7888657407407406E-3</v>
       </c>
-      <c r="B3" s="3">
-        <f t="shared" ref="B3:B22" si="0">A3*86400</f>
+      <c r="B3">
+        <f t="shared" ref="B3:B23" si="0">A3*86400</f>
         <v>240.958</v>
       </c>
       <c r="C3" s="2">
         <v>35308</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3">
         <v>35308</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" s="1">
         <v>2.7873842592592594E-3</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4">
         <f t="shared" si="0"/>
         <v>240.83</v>
       </c>
       <c r="C4" s="2">
         <v>36818</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4">
         <v>36818</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" s="1">
         <v>2.7744212962962965E-3</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5">
         <f t="shared" si="0"/>
         <v>239.71</v>
       </c>
       <c r="C5" s="2">
         <v>36818</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5">
         <v>36818</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" s="1">
         <v>2.772951388888889E-3</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6">
         <f t="shared" si="0"/>
         <v>239.58300000000003</v>
       </c>
       <c r="C6" s="2">
         <v>37469</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6">
         <v>37469</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7" s="1">
         <v>2.7462962962962962E-3</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7">
         <f t="shared" si="0"/>
         <v>237.28</v>
       </c>
       <c r="C7" s="2">
         <v>37835</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7">
         <v>37835</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8" s="1">
         <v>2.7385416666666669E-3</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8">
         <f t="shared" si="0"/>
         <v>236.61</v>
       </c>
       <c r="C8" s="2">
         <v>38221</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8">
         <v>38221</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A9" s="1">
         <v>2.7352083333333334E-3</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9">
         <f t="shared" si="0"/>
         <v>236.322</v>
       </c>
       <c r="C9" s="2">
         <v>39534</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9">
         <v>39534</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A10" s="1">
         <v>2.7222453703703705E-3</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10">
         <f t="shared" si="0"/>
         <v>235.20200000000003</v>
       </c>
       <c r="C10" s="2">
         <v>39677</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10">
         <v>39677</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A11" s="1">
         <v>2.7003935185185186E-3</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B11">
         <f t="shared" si="0"/>
         <v>233.31400000000002</v>
       </c>
       <c r="C11" s="2">
         <v>39678</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11">
         <v>39678</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A12" s="1">
         <v>2.7001736111111111E-3</v>
       </c>
-      <c r="B12" s="3">
+      <c r="B12">
         <f t="shared" si="0"/>
         <v>233.29499999999999</v>
       </c>
       <c r="C12" s="2">
         <v>41003</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12">
         <v>41003</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A13" s="1">
         <v>2.6812384259259259E-3</v>
       </c>
-      <c r="B13" s="3">
+      <c r="B13">
         <f t="shared" si="0"/>
         <v>231.65899999999999</v>
       </c>
       <c r="C13" s="2">
         <v>41124</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D13">
         <v>41124</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A14" s="1">
         <v>2.668634259259259E-3</v>
       </c>
-      <c r="B14" s="3">
+      <c r="B14">
         <f t="shared" si="0"/>
         <v>230.57</v>
       </c>
       <c r="C14" s="2">
         <v>42594</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14">
         <v>42594</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A15" s="1">
         <v>2.6651041666666663E-3</v>
       </c>
-      <c r="B15" s="3">
+      <c r="B15">
         <f t="shared" si="0"/>
         <v>230.26499999999996</v>
       </c>
       <c r="C15" s="2">
         <v>42594</v>
       </c>
-      <c r="D15" s="3">
+      <c r="D15">
         <v>42594</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A16" s="1">
         <v>2.6597685185185183E-3</v>
       </c>
-      <c r="B16" s="3">
+      <c r="B16">
         <f t="shared" si="0"/>
         <v>229.80399999999997</v>
       </c>
       <c r="C16" s="2">
         <v>43195</v>
       </c>
-      <c r="D16" s="3">
+      <c r="D16">
         <v>43195</v>
       </c>
     </row>
@@ -678,14 +677,14 @@
       <c r="A17" s="1">
         <v>2.6390277777777779E-3</v>
       </c>
-      <c r="B17" s="3">
+      <c r="B17">
         <f t="shared" si="0"/>
         <v>228.012</v>
       </c>
       <c r="C17" s="2">
         <v>43524</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17">
         <v>43524</v>
       </c>
     </row>
@@ -693,14 +692,14 @@
       <c r="A18" s="1">
         <v>2.6224421296296295E-3</v>
       </c>
-      <c r="B18" s="3">
+      <c r="B18">
         <f t="shared" si="0"/>
         <v>226.57899999999998</v>
       </c>
       <c r="C18" s="2">
         <v>43887</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18">
         <v>43887</v>
       </c>
     </row>
@@ -708,14 +707,14 @@
       <c r="A19" s="1">
         <v>2.6180902777777778E-3</v>
       </c>
-      <c r="B19" s="3">
+      <c r="B19">
         <f t="shared" si="0"/>
         <v>226.203</v>
       </c>
       <c r="C19" s="2">
         <v>43887</v>
       </c>
-      <c r="D19" s="3">
+      <c r="D19">
         <v>43887</v>
       </c>
     </row>
@@ -723,14 +722,14 @@
       <c r="A20" s="1">
         <v>2.6003703703703705E-3</v>
       </c>
-      <c r="B20" s="3">
+      <c r="B20">
         <f t="shared" si="0"/>
         <v>224.67200000000003</v>
       </c>
       <c r="C20" s="2">
         <v>43888</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20">
         <v>43888</v>
       </c>
     </row>
@@ -738,14 +737,14 @@
       <c r="A21" s="1">
         <v>2.5729976851851855E-3</v>
       </c>
-      <c r="B21" s="3">
+      <c r="B21">
         <f t="shared" si="0"/>
         <v>222.30700000000004</v>
       </c>
       <c r="C21" s="2">
         <v>44411</v>
       </c>
-      <c r="D21" s="3">
+      <c r="D21">
         <v>44411</v>
       </c>
     </row>
@@ -753,15 +752,29 @@
       <c r="A22" s="1">
         <v>2.5698148148148147E-3</v>
       </c>
-      <c r="B22" s="3">
+      <c r="B22">
         <f t="shared" si="0"/>
         <v>222.03199999999998</v>
       </c>
       <c r="C22" s="2">
         <v>44412</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22">
         <v>44412</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A23" s="1">
+        <v>2.5547453703703704E-3</v>
+      </c>
+      <c r="B23" s="3">
+        <v>220.73</v>
+      </c>
+      <c r="C23" s="2">
+        <v>45510</v>
+      </c>
+      <c r="D23" s="3">
+        <v>45510</v>
       </c>
     </row>
   </sheetData>

--- a/pages/WR_progressions/Men_TP.xlsx
+++ b/pages/WR_progressions/Men_TP.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\WR_progressions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DE5D6C3-4EC9-4C1B-A8C1-6B8EC5AF9B4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70E5F641-84BE-449B-9301-035E48F78442}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{5B864704-1F0A-4CFC-9A10-3E102D3244D3}"/>
   </bookViews>
@@ -86,11 +86,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -425,7 +424,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20BEA07D-F91B-43E2-A74E-7CB853835BEE}">
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="9.06640625" style="1"/>
@@ -468,7 +467,7 @@
         <v>2.7888657407407406E-3</v>
       </c>
       <c r="B3">
-        <f t="shared" ref="B3:B23" si="0">A3*86400</f>
+        <f t="shared" ref="B3:B22" si="0">A3*86400</f>
         <v>240.958</v>
       </c>
       <c r="C3" s="2">
@@ -767,14 +766,29 @@
       <c r="A23" s="1">
         <v>2.5547453703703704E-3</v>
       </c>
-      <c r="B23" s="3">
+      <c r="B23">
         <v>220.73</v>
       </c>
       <c r="C23" s="2">
         <v>45510</v>
       </c>
-      <c r="D23" s="3">
+      <c r="D23">
         <v>45510</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A24" s="1">
+        <v>2.5460300925925928E-3</v>
+      </c>
+      <c r="B24">
+        <v>219.99700000000001</v>
+      </c>
+      <c r="C24" s="2">
+        <v>46055</v>
+      </c>
+      <c r="D24">
+        <f>C24</f>
+        <v>46055</v>
       </c>
     </row>
   </sheetData>
